--- a/data/trans_camb/P16-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 14,25</t>
+          <t>0,24; 13,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 17,41</t>
+          <t>3,09; 16,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 20,0</t>
+          <t>6,95; 19,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 14,87</t>
+          <t>-0,47; 15,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 9,14</t>
+          <t>-6,48; 8,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 12,12</t>
+          <t>-2,84; 10,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,26</t>
+          <t>2,14; 12,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,45</t>
+          <t>2,24; 12,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,32</t>
+          <t>5,68; 14,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 38,16</t>
+          <t>0,52; 35,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 44,0</t>
+          <t>7,57; 43,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 52,4</t>
+          <t>15,12; 50,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 29,77</t>
+          <t>-0,91; 30,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 18,47</t>
+          <t>-11,01; 17,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 24,67</t>
+          <t>-4,97; 22,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 27,77</t>
+          <t>4,3; 28,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 28,4</t>
+          <t>4,53; 28,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 32,02</t>
+          <t>11,49; 33,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 17,28</t>
+          <t>2,71; 17,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 17,08</t>
+          <t>3,3; 18,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 21,83</t>
+          <t>7,44; 22,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 17,8</t>
+          <t>3,04; 17,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 10,47</t>
+          <t>-3,78; 10,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 12,01</t>
+          <t>-2,62; 11,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,78</t>
+          <t>4,17; 14,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,85</t>
+          <t>1,32; 11,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,7</t>
+          <t>4,23; 14,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 48,08</t>
+          <t>6,38; 48,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 47,19</t>
+          <t>7,74; 50,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 61,46</t>
+          <t>16,85; 61,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 36,19</t>
+          <t>5,36; 35,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 20,73</t>
+          <t>-6,79; 21,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 23,91</t>
+          <t>-4,35; 23,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 32,84</t>
+          <t>8,79; 34,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 26,89</t>
+          <t>2,71; 26,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 33,14</t>
+          <t>8,5; 31,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 20,63</t>
+          <t>9,65; 20,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 20,96</t>
+          <t>8,78; 20,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 18,96</t>
+          <t>-28,07; 19,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 22,54</t>
+          <t>3,59; 23,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 25,87</t>
+          <t>4,86; 26,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 29,18</t>
+          <t>10,12; 29,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 20,26</t>
+          <t>9,88; 20,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 21,06</t>
+          <t>10,51; 20,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 19,88</t>
+          <t>-24,46; 19,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,76; 54,23</t>
+          <t>22,05; 56,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,48; 56,03</t>
+          <t>19,95; 54,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 47,08</t>
+          <t>-64,21; 49,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 48,79</t>
+          <t>6,09; 48,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 52,97</t>
+          <t>7,98; 53,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,71; 60,44</t>
+          <t>17,03; 61,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,12; 49,74</t>
+          <t>21,29; 49,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 51,29</t>
+          <t>22,48; 50,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 45,83</t>
+          <t>-52,04; 45,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,9</t>
+          <t>3,41; 11,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 10,99</t>
+          <t>2,44; 10,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,95</t>
+          <t>5,54; 14,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 19,16</t>
+          <t>8,61; 18,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 9,48</t>
+          <t>-0,41; 9,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 31,49</t>
+          <t>6,76; 30,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,35</t>
+          <t>6,97; 13,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,27</t>
+          <t>2,88; 9,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 24,97</t>
+          <t>8,9; 25,74</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 27,52</t>
+          <t>7,23; 27,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 25,82</t>
+          <t>5,21; 25,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 32,46</t>
+          <t>11,83; 33,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,12; 37,77</t>
+          <t>14,97; 37,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 18,77</t>
+          <t>-0,74; 19,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 61,02</t>
+          <t>12,33; 58,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,49; 28,62</t>
+          <t>13,84; 28,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 20,04</t>
+          <t>5,8; 20,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,19; 53,34</t>
+          <t>18,12; 55,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,42</t>
+          <t>3,29; 17,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 16,05</t>
+          <t>2,96; 16,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 21,38</t>
+          <t>7,04; 22,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,62; 20,15</t>
+          <t>9,02; 19,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 16,08</t>
+          <t>5,48; 15,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 17,65</t>
+          <t>0,18; 16,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,62; 16,21</t>
+          <t>7,36; 15,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,25</t>
+          <t>3,89; 12,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,9</t>
+          <t>5,92; 18,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,57; 45,48</t>
+          <t>7,32; 47,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,39; 43,32</t>
+          <t>6,26; 44,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16,76; 58,33</t>
+          <t>15,36; 60,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,19; 34,83</t>
+          <t>13,95; 33,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,82; 27,62</t>
+          <t>8,58; 26,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,68; 29,4</t>
+          <t>0,27; 28,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,46; 31,48</t>
+          <t>12,98; 31,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,1; 25,94</t>
+          <t>6,81; 24,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,52; 35,2</t>
+          <t>10,59; 35,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,63; 18,89</t>
+          <t>4,62; 18,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 12,97</t>
+          <t>-0,89; 12,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 19,78</t>
+          <t>-2,12; 19,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,02</t>
+          <t>6,78; 14,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,85</t>
+          <t>3,28; 10,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,06</t>
+          <t>-4,61; 4,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,07</t>
+          <t>6,87; 14,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,59</t>
+          <t>2,24; 9,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,73</t>
+          <t>-4,98; 3,96</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20,84; 121,99</t>
+          <t>21,09; 123,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 85,94</t>
+          <t>-4,33; 80,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 110,76</t>
+          <t>-11,33; 121,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,93; 22,59</t>
+          <t>10,44; 23,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,62</t>
+          <t>5,03; 17,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 6,72</t>
+          <t>-7,1; 6,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,91; 26,26</t>
+          <t>11,98; 26,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,02; 18,01</t>
+          <t>3,98; 18,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 7,08</t>
+          <t>-8,95; 7,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,39</t>
+          <t>7,25; 12,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,82; 11,81</t>
+          <t>6,97; 12,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,67</t>
+          <t>-1,95; 13,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,82</t>
+          <t>9,33; 14,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,46</t>
+          <t>3,88; 8,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,95</t>
+          <t>4,41; 13,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,6</t>
+          <t>9,14; 12,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,6</t>
+          <t>6,13; 9,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,23</t>
+          <t>1,72; 12,08</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,12; 32,08</t>
+          <t>17,28; 31,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16,54; 30,33</t>
+          <t>16,62; 30,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 34,43</t>
+          <t>-4,22; 33,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,19; 24,12</t>
+          <t>15,6; 24,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,27; 14,58</t>
+          <t>6,57; 15,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,13; 23,93</t>
+          <t>7,45; 24,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,0; 25,81</t>
+          <t>18,19; 25,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11,95; 19,65</t>
+          <t>12,15; 19,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,77; 24,9</t>
+          <t>3,51; 24,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,31</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 13,99</t>
+          <t>0,45; 12,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,67</t>
+          <t>4,4; 17,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 19,92</t>
+          <t>6,6; 19,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 15,74</t>
+          <t>-0,66; 14,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 8,83</t>
+          <t>-5,43; 9,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 10,9</t>
+          <t>-3,29; 10,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,47</t>
+          <t>1,82; 12,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 12,23</t>
+          <t>1,46; 12,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 14,71</t>
+          <t>4,69; 14,26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 35,81</t>
+          <t>1,02; 32,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 43,39</t>
+          <t>9,69; 45,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 50,25</t>
+          <t>14,68; 50,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 30,55</t>
+          <t>-1,09; 29,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 17,61</t>
+          <t>-9,58; 19,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 22,01</t>
+          <t>-5,46; 20,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 28,17</t>
+          <t>3,86; 28,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 28,12</t>
+          <t>2,97; 28,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 33,27</t>
+          <t>9,39; 32,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 17,41</t>
+          <t>2,8; 17,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 18,2</t>
+          <t>2,94; 17,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 22,43</t>
+          <t>6,57; 21,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,83</t>
+          <t>2,69; 18,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 10,62</t>
+          <t>-4,84; 10,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 11,53</t>
+          <t>-2,16; 11,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 14,98</t>
+          <t>4,42; 15,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,63</t>
+          <t>1,81; 11,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 14,24</t>
+          <t>4,13; 14,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 48,6</t>
+          <t>6,21; 48,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 50,29</t>
+          <t>7,22; 47,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 61,73</t>
+          <t>15,27; 59,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 35,82</t>
+          <t>5,12; 36,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 21,26</t>
+          <t>-8,37; 21,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 23,38</t>
+          <t>-3,85; 22,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 34,42</t>
+          <t>8,87; 35,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 26,9</t>
+          <t>3,7; 27,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 31,86</t>
+          <t>8,39; 32,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,08</t>
+          <t>16,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,42</t>
+          <t>18,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>17,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,95</t>
+          <t>9,3; 20,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 20,78</t>
+          <t>9,04; 21,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 19,64</t>
+          <t>9,93; 22,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 23,06</t>
+          <t>4,12; 23,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 26,0</t>
+          <t>5,07; 26,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 29,28</t>
+          <t>9,03; 28,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,09</t>
+          <t>9,63; 19,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 20,81</t>
+          <t>9,44; 20,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 19,73</t>
+          <t>12,33; 22,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,0%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 56,1</t>
+          <t>21,19; 54,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,95; 54,37</t>
+          <t>20,17; 55,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 49,07</t>
+          <t>22,93; 59,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 48,37</t>
+          <t>7,18; 50,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,98; 53,67</t>
+          <t>8,31; 56,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 61,17</t>
+          <t>15,24; 61,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,29; 49,13</t>
+          <t>20,66; 48,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,48; 50,81</t>
+          <t>19,91; 49,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 45,63</t>
+          <t>25,95; 54,64</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,79</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>10,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 11,74</t>
+          <t>3,42; 11,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,8</t>
+          <t>2,46; 10,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 14,55</t>
+          <t>5,92; 14,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,9</t>
+          <t>8,03; 18,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 9,66</t>
+          <t>-0,93; 9,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 30,4</t>
+          <t>4,16; 13,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,42</t>
+          <t>7,07; 13,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 9,53</t>
+          <t>3,47; 9,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 25,74</t>
+          <t>7,09; 13,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 27,12</t>
+          <t>7,18; 27,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 25,04</t>
+          <t>5,2; 25,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 33,01</t>
+          <t>12,46; 33,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,97; 37,26</t>
+          <t>14,39; 36,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 19,15</t>
+          <t>-1,59; 18,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,33; 58,88</t>
+          <t>7,14; 27,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,84; 28,83</t>
+          <t>14,17; 28,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,65</t>
+          <t>7,07; 20,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 55,62</t>
+          <t>14,14; 29,55</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,72</t>
+          <t>8,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 17,27</t>
+          <t>3,18; 16,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,02</t>
+          <t>2,47; 15,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,04; 22,2</t>
+          <t>1,9; 15,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,37</t>
+          <t>8,54; 19,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 15,69</t>
+          <t>5,15; 15,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 16,84</t>
+          <t>2,99; 12,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 15,94</t>
+          <t>7,97; 16,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,64</t>
+          <t>4,8; 12,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 18,33</t>
+          <t>4,35; 12,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,32; 47,28</t>
+          <t>7,13; 45,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,26; 44,23</t>
+          <t>5,55; 43,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15,36; 60,27</t>
+          <t>4,89; 43,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,95; 33,62</t>
+          <t>13,09; 33,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,58; 26,85</t>
+          <t>8,04; 27,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,27; 28,31</t>
+          <t>4,58; 22,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,98; 31,22</t>
+          <t>14,06; 31,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,81; 24,66</t>
+          <t>8,55; 25,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,59; 35,46</t>
+          <t>7,87; 24,58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,62; 18,83</t>
+          <t>4,86; 18,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,84</t>
+          <t>-1,3; 12,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 19,61</t>
+          <t>-2,6; 17,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,78; 14,09</t>
+          <t>6,53; 13,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,99</t>
+          <t>2,45; 10,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 4,04</t>
+          <t>-5,32; 3,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87; 14,1</t>
+          <t>7,01; 14,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,59</t>
+          <t>2,28; 9,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,96</t>
+          <t>-4,78; 4,04</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0,49%</t>
+          <t>-1,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,81%</t>
+          <t>-0,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21,09; 123,31</t>
+          <t>22,54; 115,59</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 80,39</t>
+          <t>-8,18; 79,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 121,78</t>
+          <t>-13,67; 109,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,44; 23,25</t>
+          <t>10,05; 22,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,7</t>
+          <t>3,76; 16,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,6</t>
+          <t>-8,19; 5,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,98; 26,49</t>
+          <t>12,37; 26,88</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,98; 18,06</t>
+          <t>4,02; 17,6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 7,47</t>
+          <t>-8,57; 7,54</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,79</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>8,43</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,28</t>
+          <t>7,37; 12,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,97; 12,0</t>
+          <t>6,96; 11,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,46</t>
+          <t>9,2; 14,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,09</t>
+          <t>9,34; 14,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,66</t>
+          <t>3,98; 8,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,41; 13,94</t>
+          <t>2,72; 7,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,55</t>
+          <t>9,06; 12,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,49</t>
+          <t>6,08; 9,77</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,08</t>
+          <t>6,62; 10,03</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,28; 31,28</t>
+          <t>17,48; 31,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16,62; 30,55</t>
+          <t>16,83; 30,21</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 33,48</t>
+          <t>22,03; 37,17</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,77</t>
+          <t>15,69; 24,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,16</t>
+          <t>6,62; 15,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,45; 24,3</t>
+          <t>4,53; 12,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,19; 25,85</t>
+          <t>18,0; 25,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>12,15; 19,44</t>
+          <t>11,91; 19,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,51; 24,67</t>
+          <t>13,21; 20,61</t>
         </is>
       </c>
     </row>
